--- a/Codelist Excel Files and Conversion Templates to XML/basis.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/basis.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Codes naming the unit of work an acceptance criterion is assessed over - distinct from scope, which says which features are governed. Used for the value of the basis property of diggs:AbstractAcceptanceCriterionType, inherited by both diggs:PerformanceCriterion and diggs:DesignConformanceCriterion. Where basis expresses a per-unit-length quantum, the reference length is given by the sibling baseLength element. Extended (S14-S20 dictionary sweep) to also cover diggs:RITreatedAreaDesignType/diggs:differentialSettlementBasis, which the schema's own documentation says shares this vocabulary with AbstractAcceptanceCriterionType/basis, plus a new angular_distortion entry named in that element's documentation but previously absent from this list.</t>
+          <t>Codes naming the unit of work an acceptance criterion is assessed over - distinct from scope, which says which features are governed. Used for the value of the basis property of diggs:AbstractAcceptanceCriterionType, inherited by both diggs:PerformanceCriterion and diggs:DesignConformanceCriterion. Where basis expresses a per-unit-length quantum, the reference length is given by the sibling baseLength element. Extended (S14-S20 dictionary sweep) to also cover diggs:DesignRITreatedAreaType/diggs:differentialSettlementBasis, which the schema's own documentation says shares this vocabulary with AbstractAcceptanceCriterionType/basis, plus a new angular_distortion entry named in that element's documentation but previously absent from this list.</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>//diggs:RITreatedAreaDesign/diggs:differentialSettlementBasis</t>
+          <t>//diggs:DesignRITreatedArea/diggs:differentialSettlementBasis</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>//diggs:RITreatedAreaDesign/diggs:differentialSettlementBasis</t>
+          <t>//diggs:DesignRITreatedArea/diggs:differentialSettlementBasis</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>//diggs:RITreatedAreaDesign/diggs:differentialSettlementBasis</t>
+          <t>//diggs:DesignRITreatedArea/diggs:differentialSettlementBasis</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>//diggs:RITreatedAreaDesign/diggs:differentialSettlementBasis</t>
+          <t>//diggs:DesignRITreatedArea/diggs:differentialSettlementBasis</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>//diggs:RITreatedAreaDesign/diggs:differentialSettlementBasis</t>
+          <t>//diggs:DesignRITreatedArea/diggs:differentialSettlementBasis</t>
         </is>
       </c>
     </row>
